--- a/docs/TestCases/Vehicle_Parking_System_Test_Cases.xlsx
+++ b/docs/TestCases/Vehicle_Parking_System_Test_Cases.xlsx
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Fee follows the configured rate schedule correctly.</t>
+          <t>For the specified entry time, exit time, and configured rate schedule, the calculated fee equals the expected amount calculated from the applicable rate and parking duration.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1046,7 +1046,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>The SRS gives the fee rule as correct rate × duration but does not define a concrete rate table, boundary inclusivity, rounding, or minimum charge. Record the exact schedule and expected amount in test data before execution.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1086,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Payment status becomes successful.</t>
+          <t>After the payment service returns a confirmed successful result, the system records payment as successful and permits the exit barrier to open.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1095,7 +1099,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Aligned to VPS-F-008: payment must be confirmed before the exit barrier opens. Use a controlled sandbox/mock response and verify both the recorded status and barrier command.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1135,7 +1143,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>System records failure and does not complete paid exit.</t>
+          <t>The system records the payment as failed, does not mark the fee as paid, and keeps the exit barrier closed.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1144,7 +1152,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Aligned to VPS-F-008 acceptance criterion that failed payment prevents exit. Verify that a declined payment does not create a successful payment record.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1184,7 +1196,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>System handles timeout/error without corrupting parking/payment state.</t>
+          <t>When the payment gateway times out or returns an unavailable response, the system displays/records a payment error, does not mark the payment successful, and does not open the exit barrier without confirmed payment.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1193,7 +1205,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>The SRS specifies retry/backoff for failed API calls, but does not define the exact retry count or timeout. Those values need to be agreed before testing. Keep the test in a controlled mock/sandbox environment.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1233,7 +1249,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Receipt contains ticket, duration, amount and payment status.</t>
+          <t>After successful payment, the receipt is printed or sent digitally and contains the ticket ID, parking duration, amount paid, and payment timestamp.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1242,7 +1258,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Aligned to VPS-F-009 acceptance criterion. The current test data should include known ticket ID, duration, amount, and payment timestamp for comparison.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1282,7 +1302,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Slot becomes available and parking record is closed.</t>
+          <t>After vehicle exit is confirmed, the parking slot changes to Available within 5 seconds and the parking record is closed.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1291,7 +1311,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>The SRS explicitly requires the slot to return to Available within 5 seconds of exit confirmation. Define how exit confirmation and slot state are observed in the test environment.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1342,7 +1366,9 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>SRS §4.3 describes ticket validation generally, but does not define a dedicated requirement ID or explicit acceptance criterion for rejecting an invalid ticket. The previous mapping to VPS-F-010 is incorrect because VPS-F-010 concerns marking the parking slot Available after confirmed vehicle exit. Keep this test pending clarification; confirm the requirement and expected behavior with the team/lecturer.</t>
+          <t>SRS §4.3 describes ticket validation generally, but does not define a dedicated requirement ID or explicit acceptance criterion for rejecting an invalid ticket. The previous mapping to VPS-F-010 is incorrect because VPS-F-010 concerns marking the parking slot Available after confirmed vehicle exit. Keep this test pending clarification; confirm the requirement and expected behavior with the team/lecturer.
+Keep pending clarification. SRS §4.3 describes ticket validation generally but does not define a dedicated requirement ID or explicit acceptance criterion for rejecting an invalid ticket.
+SRS §4.3 describes ticket validation generally but does not define a dedicated requirement ID or explicit acceptance criterion for rejecting an invalid ticket. Do not map this case to VPS-F-010, which concerns slot release.</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1410,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Reservation is created with correct status and time window.</t>
+          <t>A registered customer receives a confirmed reservation containing a booking ID and slot number for the requested time window; the slot is held until 15 minutes after the specified arrival time.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1393,7 +1419,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Aligned to VPS-F-011 acceptance criteria. Ensure the test uses a registered customer account and records the specified arrival time so the 15-minute hold can be verified.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1433,7 +1463,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Conflicting reservation is rejected.</t>
+          <t>A second reservation request for the same slot and an overlapping time window is rejected, and the existing reservation remains unchanged.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1442,7 +1472,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>The SRS does not spell out this negative acceptance case in detail. Confirm the intended conflict/overlap rule with the team, especially whether partial overlaps are prohibited.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1482,7 +1516,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Reservation is released and slot becomes available according to rules.</t>
+          <t>If the customer has not arrived within the reservation grace period, the reserved slot is released and its status changes to Available after the 15-minute post-arrival grace period expires.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1491,7 +1525,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>VPS-F-011 specifies that the slot is held for 15 minutes past arrival time, and VPS-F-012 requires automatic release after grace-period expiry. Define a controllable test clock or reliable way to simulate expiry.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1531,7 +1569,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Dashboard displays current occupancy and relevant parking data.</t>
+          <t>The dashboard displays the current occupancy information supported by the approved SRS and the available test data.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1540,7 +1578,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Clarification needed: identify the exact dashboard fields and expected values from the SRS/UI specification before execution. Use a known set of occupied and available slots to verify displayed values.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1589,7 +1631,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Confirm that vehicle/history search is explicitly in scope for VPS-F-013. If the SRS does not specify this function, record it as a proposed test or obtain an approved requirement mapping rather than assuming coverage.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1629,7 +1675,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Rate is saved and used by fee calculation.</t>
+          <t>After an authorized admin saves a valid rate schedule, the saved values are displayed when the rate settings are reopened and are used by a subsequent fee calculation.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1638,7 +1684,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Use a concrete rate schedule with known values. Confirm the SRS-defined fields and effective-time behavior before execution.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1687,7 +1737,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>The SRS/test materials do not define all invalid-rate rules (such as negative values, zero values, or overlapping time ranges). Confirm which inputs must be rejected and document the expected validation response.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1727,7 +1781,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Requested file is generated with correct report data.</t>
+          <t>The selected report is exported in the chosen CSV or PDF format, opens successfully, and contains the expected records and field values for the selected reporting period.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1736,7 +1790,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Use a small known dataset and verify record count, key field values, date range, and file format. Confirm which report fields are required by the SRS.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1785,7 +1843,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>The SRS target is transaction response time ≤5 seconds at the 90th percentile. Define the transaction mix, concurrency, data volume, test duration, environment, and measurement method before execution; 'representative load' alone is not reproducible.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1825,7 +1887,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Observed availability supports the 99.9% monthly target or exceptions are documented.</t>
+          <t>The measured availability for the defined observation period is calculated from recorded uptime and downtime, with planned maintenance handled according to the agreed measurement rule.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1834,7 +1896,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>The SRS target is 99.9% monthly availability. A short test window cannot establish monthly compliance by itself. Treat this as an evidence/monitoring check unless a full representative measurement period is available.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1874,7 +1940,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>No plaintext card number is stored or logged.</t>
+          <t>No full payment-card number or sensitive authentication data is present in the application database, logs, or stored payment records after the sandbox payment flow.</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1883,7 +1949,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>This test checks for plaintext sensitive payment data only; it does not establish full PCI-DSS compliance. Use only sandbox payment data and approved inspection access.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1923,7 +1993,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Retention configuration supports minimum 5-year requirement.</t>
+          <t>The configured audit-log retention policy is set to at least five years, and the team provides evidence that stored audit records are subject to that policy.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1932,7 +2002,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>A configuration inspection does not prove that records are actually retained for five years. Record this as configuration evidence unless retention history or an approved retention-control test is available.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1972,7 +2046,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>UI meets applicable WCAG 2.1 AA checks defined for the project.</t>
+          <t>For the agreed representative pages, keyboard-only users can reach and operate all tested controls, visible focus is present, form controls have programmatic labels, and documented contrast checks meet the project's WCAG 2.1 AA criteria.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1981,7 +2055,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Define the page/sample list, browser, assistive-technology approach if applicable, contrast tool, and pass/fail evidence. A small manual check does not prove full WCAG 2.1 AA conformance.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2021,7 +2099,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Applicable network communication uses TLS 1.2 or higher.</t>
+          <t>Each in-scope network endpoint tested negotiates TLS 1.2 or higher; insecure protocol versions are disabled.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2030,7 +2108,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>List the endpoints and test method used. A single endpoint check does not prove that every communication path uses TLS 1.2+.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2070,7 +2152,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Weak password is rejected; compliant password is accepted.</t>
+          <t>Passwords that violate the approved password policy are rejected, and passwords that satisfy the policy are accepted.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2079,7 +2161,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>The SRS requires password complexity but the case does not state the exact policy rules. Obtain the approved minimum length/character rules and use explicit weak and compliant examples.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2119,7 +2205,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Each role can access only permitted functions.</t>
+          <t>Admin, attendant, and customer accounts can perform their permitted actions, while attempts to access restricted functions are denied.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2128,7 +2214,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Prepare a role-permission matrix from the SRS before execution and record at least one allowed and one denied action for each role.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2168,7 +2258,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Account is locked according to policy and event is audited.</t>
+          <t>After five consecutive failed login attempts, the account is locked according to the approved policy, further login attempts are blocked, and the lockout event is recorded.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2177,7 +2267,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Confirm the expected lockout duration, unlock/recovery behavior, and whether the counter resets after a successful login; those details are not specified in this test case.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2217,7 +2311,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Protected-at-rest mechanism is configured for applicable sensitive records.</t>
+          <t>Evidence confirms that applicable stored data is protected at rest using AES-256, as required by the STP security requirement.</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2226,7 +2320,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>The original expected result only checked for a generic protected-at-rest mechanism, which is insufficient for the stated AES-256 requirement. Verify the actual approved storage/encryption configuration; do not inspect or expose production secrets.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2236,7 +2334,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>VPS-F-003</t>
+          <t>VPS-F-001/VPS-F-002/VPS-F-003</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2266,7 +2364,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Entry workflow completes and consistent state is stored.</t>
+          <t>A vehicle entry flow captures or accepts the plate, assigns one available slot, creates a ticket with consistent vehicle/slot details, and opens the barrier only after the entry workflow succeeds.</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2275,7 +2373,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>This is an integration scenario spanning plate capture, slot allocation, and ticket creation. Keep the detailed individual checks in TC-001, TC-004, and TC-006; verify that the resulting records agree.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2285,7 +2387,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>VPS-F-007/VPS-F-008/VPS-F-010</t>
+          <t>VPS-F-007/VPS-F-008/VPS-F-009/VPS-F-010</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2315,7 +2417,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Exit completes only after successful payment and final state is consistent.</t>
+          <t>Exit is completed only after the ticket is validated, the fee is calculated, payment is confirmed, a receipt is generated, the exit is confirmed, and the slot is released; the stored final state is consistent.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2324,7 +2426,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>The original mapping omitted VPS-F-009 even though the steps include receipt generation. This end-to-end scenario does not replace the individual fee, payment, receipt, and slot-release tests.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2334,7 +2440,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>VPS-F-002/VPS-F-010</t>
+          <t>VPS-F-002</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2364,7 +2470,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Only one request obtains the slot; no double allocation occurs.</t>
+          <t>For two concurrent requests competing for the same single available slot, exactly one request succeeds and the slot is associated with only one vehicle.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2373,7 +2479,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Removed VPS-F-010 from the mapping because this scenario tests allocation concurrency, not slot release. Define how concurrency is triggered and how the final slot assignment is verified.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2383,7 +2493,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>VPS-F-013/VPS-F-015</t>
+          <t>VPS-SR-003/VPS-F-015</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2413,7 +2523,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Access is denied and event is handled according to security policy.</t>
+          <t>A non-admin account is denied access to the report-export function through both the UI and any directly accessible export endpoint; no report file is returned.</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2422,7 +2532,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>The original mapping to VPS-F-013 (admin dashboard) was not directly tested by this case. The security mapping is role-based access control; retain VPS-F-015 only if report export is explicitly part of that functional requirement.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2462,7 +2576,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Final slot is allocated once; subsequent entry is blocked.</t>
+          <t>With one slot remaining, the first vehicle is assigned that slot and occupancy reaches capacity; a subsequent entry attempt is blocked, no additional slot is allocated, and displayed availability remains zero.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2471,7 +2585,11 @@
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>This boundary scenario overlaps with TC-006/F-003 only if ticket creation is checked. Keep its primary coverage mapped to full-capacity handling and availability; verify state after both attempts.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K40"/>
